--- a/output/pdf_financials_xlsx/CGO.xlsx
+++ b/output/pdf_financials_xlsx/CGO.xlsx
@@ -1279,7 +1279,7 @@
         <v>264.93</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>346.565</v>
+        <v>-183.865</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-82.376</v>
@@ -1579,7 +1579,7 @@
         <v>210.17</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>265.215</v>
+        <v>-265.215</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-158.705</v>
@@ -1753,7 +1753,7 @@
         <v>210.17</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>265.215</v>
+        <v>-265.215</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-158.705</v>
@@ -1937,7 +1937,7 @@
         <v>52.281095</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>49.852444</v>
+        <v>-49.852444</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>90.688571</v>
@@ -1997,7 +1997,7 @@
         <v>264.93</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>346.565</v>
+        <v>-183.865</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-82.376</v>
@@ -2113,7 +2113,7 @@
         <v>730.578</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>819.1799999999999</v>
+        <v>288.75</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>419.794</v>
@@ -2171,7 +2171,7 @@
         <v>34.8551886940981</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>37.45399862744569</v>
+        <v>13.20203386761755</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>18.19335417350155</v>
@@ -2229,7 +2229,7 @@
         <v>20.6696108405994</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>23.47323012999004</v>
+        <v>-44.24441845919561</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-92.65926969020103</v>
@@ -2287,7 +2287,7 @@
         <v>10.0270128690415</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>12.12598237991407</v>
+        <v>-12.12598237991407</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>-6.878078948497509</v>
@@ -5765,46 +5765,46 @@
         <v>3.488</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.338</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.007</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.858</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.468</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>7.349</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>7.644</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>9.147</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>9.164999999999999</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>11.12</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>9.94</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>11.031</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>10.38</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>12.493</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>12.302</v>
       </c>
     </row>
     <row r="93">
@@ -6135,13 +6135,13 @@
         <v>210.17</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>265.215</v>
+        <v>-265.215</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-158.705</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>313.367</v>
+        <v>-313.367</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>375.569</v>
@@ -10674,7 +10674,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -16092,7 +16096,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -17989,7 +17997,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -39058,13 +39070,13 @@
         </is>
       </c>
       <c r="K317" s="5" t="n">
-        <v>265.215</v>
+        <v>-265.215</v>
       </c>
       <c r="L317" s="5" t="n">
         <v>-158.705</v>
       </c>
       <c r="M317" s="5" t="n">
-        <v>313.367</v>
+        <v>-313.367</v>
       </c>
       <c r="N317" t="inlineStr">
         <is>
@@ -53394,7 +53406,7 @@
         <v>-46.872</v>
       </c>
       <c r="H464" s="5" t="n">
-        <v>229.692</v>
+        <v>-229.692</v>
       </c>
       <c r="I464" t="inlineStr">
         <is>
@@ -53407,13 +53419,13 @@
         </is>
       </c>
       <c r="K464" s="5" t="n">
-        <v>265.215</v>
+        <v>-265.215</v>
       </c>
       <c r="L464" s="5" t="n">
         <v>-158.705</v>
       </c>
       <c r="M464" s="5" t="n">
-        <v>313.367</v>
+        <v>-313.367</v>
       </c>
       <c r="N464" t="inlineStr">
         <is>
@@ -57215,7 +57227,7 @@
         <v>-0.00095</v>
       </c>
       <c r="H503" s="5" t="n">
-        <v>0.00461</v>
+        <v>-0.00461</v>
       </c>
       <c r="I503" t="inlineStr">
         <is>
@@ -57417,7 +57429,7 @@
         <v>-0.00095</v>
       </c>
       <c r="H505" s="5" t="n">
-        <v>0.00458</v>
+        <v>-0.00458</v>
       </c>
       <c r="I505" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CGO.xlsx
+++ b/output/pdf_financials_xlsx/CGO.xlsx
@@ -6892,31 +6892,31 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>2.644</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>9.741</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>2.467</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>8.249000000000001</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>2.564</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>4.529</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>2.653</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>3.381</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>0</v>
@@ -30784,7 +30784,11 @@
           <t>Proceeds on disposals of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -35440,7 +35444,11 @@
           <t>Proceeds on disposals of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CGO.xlsx
+++ b/output/pdf_financials_xlsx/CGO.xlsx
@@ -6123,7 +6123,7 @@
         <v>56.264</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>-46.872</v>
+        <v>-8.978999999999999</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>0.00461</v>
@@ -45172,7 +45172,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E379" s="5" t="n">
         <v>-79.014</v>
       </c>
@@ -45568,7 +45572,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E383" s="5" t="n">
         <v>2.562</v>
       </c>
